--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487985_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487985_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.6786</v>
+        <v>3.0952</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6911</v>
+        <v>2.6975</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.3978</v>
       </c>
       <c r="G2" t="n">
         <v>0.3</v>
@@ -610,13 +610,13 @@
         <v>3.568</v>
       </c>
       <c r="S2" t="n">
-        <v>5.8363</v>
+        <v>2.2529</v>
       </c>
       <c r="T2" t="n">
-        <v>5.0001</v>
+        <v>2.0064</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8362000000000001</v>
+        <v>0.2466</v>
       </c>
       <c r="V2" t="n">
         <v>0.1459</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4693</v>
+        <v>2.4347</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4873</v>
+        <v>1.0985</v>
       </c>
       <c r="F3" t="n">
-        <v>1.982</v>
+        <v>1.3362</v>
       </c>
       <c r="G3" t="n">
         <v>3.039</v>
@@ -688,13 +688,13 @@
         <v>2.3787</v>
       </c>
       <c r="S3" t="n">
-        <v>0.553</v>
+        <v>0.5184</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9984</v>
+        <v>-0.3871</v>
       </c>
       <c r="U3" t="n">
-        <v>1.5513</v>
+        <v>0.9055</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5281</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>F. CHEKRI KOURAYCHE</t>
+          <t>W. EL OTMANI MOHAMED</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3948</v>
+        <v>1.9263</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5167</v>
+        <v>1.1881</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8781</v>
+        <v>0.7382</v>
       </c>
       <c r="G4" t="n">
-        <v>2.7915</v>
+        <v>0.1109</v>
       </c>
       <c r="H4" t="n">
-        <v>7.23</v>
+        <v>0.5201</v>
       </c>
       <c r="I4" t="n">
-        <v>-4.4385</v>
+        <v>-0.4093</v>
       </c>
       <c r="J4" t="n">
-        <v>3.7448</v>
+        <v>0.3554</v>
       </c>
       <c r="K4" t="n">
-        <v>7.1365</v>
+        <v>0.5044</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.3918</v>
+        <v>-0.149</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.9533</v>
+        <v>-0.2446</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0934</v>
+        <v>0.0157</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0467</v>
+        <v>-0.2602</v>
       </c>
       <c r="P4" t="n">
-        <v>-5.1538</v>
+        <v>0.3964</v>
       </c>
       <c r="Q4" t="n">
-        <v>-8.1272</v>
+        <v>-0.9911</v>
       </c>
       <c r="R4" t="n">
-        <v>2.9733</v>
+        <v>1.3876</v>
       </c>
       <c r="S4" t="n">
-        <v>3.208</v>
+        <v>-0.3212</v>
       </c>
       <c r="T4" t="n">
-        <v>2.9627</v>
+        <v>0.08359999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2453</v>
+        <v>-0.4048</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5491</v>
+        <v>1.7403</v>
       </c>
       <c r="W4" t="n">
-        <v>1.9364</v>
+        <v>1.7403</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3873</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>W. EL OTMANI MOHAMED</t>
+          <t>T. LIBERATORE DARGAM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1019</v>
+        <v>1.1483</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6163999999999999</v>
+        <v>-0.0153</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4855</v>
+        <v>1.1636</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1109</v>
+        <v>-1.3101</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5201</v>
+        <v>-1.1742</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4093</v>
+        <v>-0.1358</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3554</v>
+        <v>-1.3179</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5044</v>
+        <v>-0.6388</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.149</v>
+        <v>-0.6791</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.2446</v>
+        <v>0.0078</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0157</v>
+        <v>-0.5355</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2602</v>
+        <v>0.5433</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3964</v>
+        <v>1.1893</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3876</v>
+        <v>1.1893</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1457</v>
+        <v>0.1826</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4881</v>
+        <v>0.0955</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6575</v>
+        <v>0.0871</v>
       </c>
       <c r="V5" t="n">
-        <v>1.7403</v>
+        <v>1.0864</v>
       </c>
       <c r="W5" t="n">
-        <v>1.7403</v>
+        <v>1.2071</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. LIBERATORE DARGAM</t>
+          <t>F. CHEKRI KOURAYCHE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7127</v>
+        <v>0.4386</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4228</v>
+        <v>-1.4583</v>
       </c>
       <c r="F6" t="n">
-        <v>1.1355</v>
+        <v>1.8969</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3101</v>
+        <v>2.7915</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1742</v>
+        <v>7.23</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1358</v>
+        <v>-4.4385</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.3179</v>
+        <v>3.7448</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6388</v>
+        <v>7.1365</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6791</v>
+        <v>-3.3918</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0078</v>
+        <v>-0.9533</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5355</v>
+        <v>0.0934</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5433</v>
+        <v>-1.0467</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1893</v>
+        <v>-5.1538</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-8.1272</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1893</v>
+        <v>2.9733</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2529</v>
+        <v>1.2517</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.312</v>
+        <v>0.9877</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0591</v>
+        <v>0.2641</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0864</v>
+        <v>1.5491</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2071</v>
+        <v>1.9364</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1207</v>
+        <v>-0.3873</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. VICENTE BOSCH</t>
+          <t>S. CURBELO MENENDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3275</v>
+        <v>-1.6985</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9126</v>
+        <v>-1.6049</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4148</v>
+        <v>-0.0936</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.1314</v>
+        <v>-2.7467</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7348</v>
+        <v>0.08459999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.3966</v>
+        <v>-2.8314</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5382</v>
+        <v>-1.1706</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0605</v>
+        <v>0.3367</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5988</v>
+        <v>-1.5073</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.5932</v>
+        <v>-1.5761</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7953</v>
+        <v>-0.252</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-1.3241</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7929</v>
+        <v>0.3964</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1893</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7929</v>
+        <v>1.5858</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8682</v>
+        <v>0.3147</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3744</v>
+        <v>0.1515</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4938</v>
+        <v>0.1632</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1207</v>
+        <v>0.337</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1207</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S. CURBELO MENENDEZ</t>
+          <t>J. VICENTE BOSCH</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.6924</v>
+        <v>-2.3036</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.318</v>
+        <v>-0.7484</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3744</v>
+        <v>-1.5552</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.7467</v>
+        <v>-2.1314</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08459999999999999</v>
+        <v>-0.7348</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.8314</v>
+        <v>-1.3966</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1706</v>
+        <v>-0.5382</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3367</v>
+        <v>0.0605</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.5073</v>
+        <v>-0.5988</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5761</v>
+        <v>-1.5932</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.252</v>
+        <v>-0.7953</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3241</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3964</v>
+        <v>0.7929</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1893</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5858</v>
+        <v>0.7929</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6791</v>
+        <v>-0.8443000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5616</v>
+        <v>-0.2101</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1176</v>
+        <v>-0.6342</v>
       </c>
       <c r="V8" t="n">
-        <v>0.337</v>
+        <v>-0.1207</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2666</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.823</v>
+        <v>-5.2575</v>
       </c>
       <c r="E9" t="n">
-        <v>-6.5286</v>
+        <v>-6.0193</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7057</v>
+        <v>0.7618</v>
       </c>
       <c r="G9" t="n">
         <v>-1.8394</v>
@@ -1156,13 +1156,13 @@
         <v>2.1805</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2981</v>
+        <v>0.8636</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2534</v>
+        <v>0.7627</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0447</v>
+        <v>0.1008</v>
       </c>
       <c r="V9" t="n">
         <v>0.674</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-7.2205</v>
+        <v>-6.2765</v>
       </c>
       <c r="E10" t="n">
-        <v>-7.3533</v>
+        <v>-6.5778</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1328</v>
+        <v>0.3013</v>
       </c>
       <c r="G10" t="n">
         <v>-2.3551</v>
@@ -1234,13 +1234,13 @@
         <v>1.9822</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9009</v>
+        <v>0.0431</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3634</v>
+        <v>0.4121</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.5375</v>
+        <v>-0.369</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.7061</v>
+        <v>-6.493</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.2238</v>
+        <v>-11.4399</v>
       </c>
       <c r="F11" t="n">
-        <v>5.517799999999999</v>
+        <v>4.947</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.141299999999999</v>
+        <v>-4.1413</v>
       </c>
       <c r="H11" t="n">
         <v>8.4739</v>
@@ -1285,7 +1285,7 @@
         <v>-12.6153</v>
       </c>
       <c r="J11" t="n">
-        <v>5.029300000000001</v>
+        <v>5.0293</v>
       </c>
       <c r="K11" t="n">
         <v>12.0148</v>
@@ -1300,7 +1300,7 @@
         <v>-3.5409</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.629600000000001</v>
+        <v>-5.6296</v>
       </c>
       <c r="P11" t="n">
         <v>-11.4972</v>
@@ -1312,19 +1312,19 @@
         <v>18.0383</v>
       </c>
       <c r="S11" t="n">
-        <v>6.048599999999999</v>
+        <v>4.261500000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>5.118299999999999</v>
+        <v>3.9023</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9302000000000002</v>
+        <v>0.3593</v>
       </c>
       <c r="V11" t="n">
         <v>4.8839</v>
       </c>
       <c r="W11" t="n">
-        <v>9.164100000000001</v>
+        <v>9.164099999999999</v>
       </c>
       <c r="X11" t="n">
         <v>-4.2802</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>M. HETOR MENSAH</t>
+          <t>A. ARTILES AGUILAR</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.1483</v>
+        <v>4.7897</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8232</v>
+        <v>1.6292</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3251</v>
+        <v>3.1605</v>
       </c>
       <c r="G12" t="n">
-        <v>2.4794</v>
+        <v>2.9928</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3253</v>
+        <v>0.3834</v>
       </c>
       <c r="I12" t="n">
-        <v>2.8047</v>
+        <v>2.6095</v>
       </c>
       <c r="J12" t="n">
-        <v>2.982</v>
+        <v>3.1657</v>
       </c>
       <c r="K12" t="n">
-        <v>1.0094</v>
+        <v>1.1167</v>
       </c>
       <c r="L12" t="n">
-        <v>1.9726</v>
+        <v>2.0491</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.5027</v>
+        <v>-0.1729</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.3347</v>
+        <v>-0.7333</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8321</v>
+        <v>0.5604</v>
       </c>
       <c r="P12" t="n">
-        <v>1.784</v>
+        <v>1.9822</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.1716</v>
+        <v>-1.9822</v>
       </c>
       <c r="R12" t="n">
-        <v>4.9556</v>
+        <v>3.9645</v>
       </c>
       <c r="S12" t="n">
-        <v>1.076</v>
+        <v>0.2019</v>
       </c>
       <c r="T12" t="n">
-        <v>1.4796</v>
+        <v>0.1791</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4036</v>
+        <v>0.0228</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1911</v>
+        <v>-0.3873</v>
       </c>
       <c r="W12" t="n">
-        <v>0.5331</v>
+        <v>0.2666</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.7243000000000001</v>
+        <v>-0.6539</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. ARTILES AGUILAR</t>
+          <t>M. HETOR MENSAH</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.5405</v>
+        <v>4.1577</v>
       </c>
       <c r="E13" t="n">
-        <v>0.7123</v>
+        <v>0.8045</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8282</v>
+        <v>3.3532</v>
       </c>
       <c r="G13" t="n">
-        <v>2.9928</v>
+        <v>2.4794</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3834</v>
+        <v>-0.3253</v>
       </c>
       <c r="I13" t="n">
-        <v>2.6095</v>
+        <v>2.8047</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1657</v>
+        <v>2.982</v>
       </c>
       <c r="K13" t="n">
-        <v>1.1167</v>
+        <v>1.0094</v>
       </c>
       <c r="L13" t="n">
-        <v>2.0491</v>
+        <v>1.9726</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1729</v>
+        <v>-0.5027</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7333</v>
+        <v>-1.3347</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5604</v>
+        <v>0.8321</v>
       </c>
       <c r="P13" t="n">
-        <v>1.9822</v>
+        <v>1.784</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.9822</v>
+        <v>-3.1716</v>
       </c>
       <c r="R13" t="n">
-        <v>3.9645</v>
+        <v>4.9556</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0473</v>
+        <v>0.0854</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7377</v>
+        <v>0.4609</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3095</v>
+        <v>-0.3755</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3873</v>
+        <v>-0.1911</v>
       </c>
       <c r="W13" t="n">
-        <v>0.2666</v>
+        <v>0.5331</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.6539</v>
+        <v>-0.7243000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5518</v>
+        <v>1.8326</v>
       </c>
       <c r="E14" t="n">
         <v>-1.44</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9918</v>
+        <v>3.2726</v>
       </c>
       <c r="G14" t="n">
         <v>-0.9939</v>
@@ -1546,13 +1546,13 @@
         <v>5.1538</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.1966</v>
+        <v>-0.9157999999999999</v>
       </c>
       <c r="T14" t="n">
         <v>-0.2017</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9949</v>
+        <v>-0.7141</v>
       </c>
       <c r="V14" t="n">
         <v>2.7512</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3811</v>
+        <v>1.5108</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1571</v>
+        <v>0.8702</v>
       </c>
       <c r="F15" t="n">
-        <v>0.224</v>
+        <v>0.6405999999999999</v>
       </c>
       <c r="G15" t="n">
         <v>1.1301</v>
@@ -1624,13 +1624,13 @@
         <v>1.9822</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.6372</v>
+        <v>-0.5075</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1121</v>
+        <v>-0.399</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.525</v>
+        <v>-0.1084</v>
       </c>
       <c r="V15" t="n">
         <v>1.0864</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.261</v>
+        <v>-0.1014</v>
       </c>
       <c r="E16" t="n">
-        <v>-2.5816</v>
+        <v>-2.3778</v>
       </c>
       <c r="F16" t="n">
-        <v>2.8426</v>
+        <v>2.2764</v>
       </c>
       <c r="G16" t="n">
         <v>-1.3424</v>
@@ -1702,13 +1702,13 @@
         <v>4.3609</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6297</v>
+        <v>-0.9921</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8184</v>
+        <v>-0.6147</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1887</v>
+        <v>-0.3774</v>
       </c>
       <c r="V16" t="n">
         <v>-1.1367</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0315</v>
+        <v>-0.2959</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0341</v>
+        <v>-0.1696</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.1263</v>
       </c>
       <c r="G17" t="n">
         <v>1.1284</v>
@@ -1780,13 +1780,13 @@
         <v>1.3876</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2544</v>
+        <v>-0.0101</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3782</v>
+        <v>0.1744</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1238</v>
+        <v>-0.1845</v>
       </c>
       <c r="V17" t="n">
         <v>-1.8107</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. SANCHES CARDOSO MENDES</t>
+          <t>B. EDOKPAYI MANCERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.4036</v>
+        <v>-0.5327</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2472</v>
+        <v>-1.1083</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8436</v>
+        <v>0.5756</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.2631</v>
+        <v>0.9779</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.3548</v>
+        <v>-0.7057</v>
       </c>
       <c r="I18" t="n">
-        <v>0.09180000000000001</v>
+        <v>1.6836</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.6071</v>
+        <v>1.488</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.6875</v>
+        <v>0.761</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0804</v>
+        <v>0.7271</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.656</v>
+        <v>-0.5101</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6674</v>
+        <v>-1.4666</v>
       </c>
       <c r="O18" t="n">
-        <v>0.0114</v>
+        <v>0.9565</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5947</v>
+        <v>0.7929</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9911</v>
+        <v>-1.9822</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5858</v>
+        <v>2.7751</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1852</v>
+        <v>-0.6387</v>
       </c>
       <c r="T18" t="n">
-        <v>1.351</v>
+        <v>0.0598</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8342000000000001</v>
+        <v>-0.6985</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9204</v>
+        <v>-1.6648</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.9204</v>
+        <v>-0.9908</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. EDOKPAYI MANCERA</t>
+          <t>E. EGEA SOLER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2268</v>
+        <v>-1.366</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.414</v>
+        <v>-1.7732</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1871</v>
+        <v>0.4072</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9779</v>
+        <v>0.06710000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.7057</v>
+        <v>-1.3046</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6836</v>
+        <v>1.3717</v>
       </c>
       <c r="J19" t="n">
-        <v>1.488</v>
+        <v>0.6471</v>
       </c>
       <c r="K19" t="n">
-        <v>0.761</v>
+        <v>-0.0398</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7271</v>
+        <v>0.6869</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5101</v>
+        <v>-0.58</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4666</v>
+        <v>-1.2648</v>
       </c>
       <c r="O19" t="n">
-        <v>0.9565</v>
+        <v>0.6848</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7929</v>
+        <v>1.1893</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9822</v>
+        <v>-2.1805</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7751</v>
+        <v>3.3698</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3329</v>
+        <v>-1.4857</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2458</v>
+        <v>-0.5064</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0871</v>
+        <v>-0.9792999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.6648</v>
+        <v>-1.1367</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.674</v>
+        <v>0.2666</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9908</v>
+        <v>-1.4033</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. EGEA SOLER</t>
+          <t>R. SANCHES CARDOSO MENDES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6749</v>
+        <v>-1.8996</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7732</v>
+        <v>-2.2659</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0983</v>
+        <v>0.3663</v>
       </c>
       <c r="G20" t="n">
-        <v>0.06710000000000001</v>
+        <v>-2.2631</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.3046</v>
+        <v>-2.3548</v>
       </c>
       <c r="I20" t="n">
-        <v>1.3717</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6471</v>
+        <v>-1.6071</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.0398</v>
+        <v>-1.6875</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6869</v>
+        <v>0.0804</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.58</v>
+        <v>-0.656</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2648</v>
+        <v>-0.6674</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6848</v>
+        <v>0.0114</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1893</v>
+        <v>0.5947</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1805</v>
+        <v>-0.9911</v>
       </c>
       <c r="R20" t="n">
-        <v>3.3698</v>
+        <v>1.5858</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7946</v>
+        <v>0.6892</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5064</v>
+        <v>0.3323</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.2882</v>
+        <v>0.3569</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1367</v>
+        <v>-0.9204</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4033</v>
+        <v>-0.9204</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.7436</v>
+        <v>-4.5118</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5279</v>
+        <v>-2.3242</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2157</v>
+        <v>-2.1876</v>
       </c>
       <c r="G21" t="n">
         <v>-0.5649</v>
@@ -2092,13 +2092,13 @@
         <v>0.1982</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7228</v>
+        <v>-0.491</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3744</v>
+        <v>-0.1706</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3484</v>
+        <v>-0.3203</v>
       </c>
       <c r="V21" t="n">
         <v>-1.4737</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>2.802300000000001</v>
+        <v>3.583400000000002</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.257200000000001</v>
+        <v>-8.155099999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>11.0594</v>
+        <v>11.7385</v>
       </c>
       <c r="G22" t="n">
         <v>3.6114</v>
@@ -2143,22 +2143,22 @@
         <v>12.1105</v>
       </c>
       <c r="J22" t="n">
-        <v>9.0639</v>
+        <v>9.063900000000002</v>
       </c>
       <c r="K22" t="n">
         <v>3.8589</v>
       </c>
       <c r="L22" t="n">
-        <v>5.204999999999999</v>
+        <v>5.205</v>
       </c>
       <c r="M22" t="n">
-        <v>-5.4526</v>
+        <v>-5.452599999999999</v>
       </c>
       <c r="N22" t="n">
         <v>-12.3579</v>
       </c>
       <c r="O22" t="n">
-        <v>6.905500000000001</v>
+        <v>6.9055</v>
       </c>
       <c r="P22" t="n">
         <v>8.92</v>
@@ -2170,22 +2170,22 @@
         <v>29.7335</v>
       </c>
       <c r="S22" t="n">
-        <v>-4.8455</v>
+        <v>-4.064399999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7877000000000001</v>
+        <v>-0.6859000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-4.0576</v>
+        <v>-3.3783</v>
       </c>
       <c r="V22" t="n">
-        <v>-4.883800000000001</v>
+        <v>-4.8838</v>
       </c>
       <c r="W22" t="n">
         <v>4.2802</v>
       </c>
       <c r="X22" t="n">
-        <v>-9.164100000000001</v>
+        <v>-9.164099999999999</v>
       </c>
     </row>
   </sheetData>
